--- a/prudential-bank-corrected-package/parsed-excel/Prudential bank(0091900180008)_sep 23[10235] - parsed.xlsx
+++ b/prudential-bank-corrected-package/parsed-excel/Prudential bank(0091900180008)_sep 23[10235] - parsed.xlsx
@@ -32,10 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -399,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G293"/>
+  <dimension ref="A1:G409"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +425,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-17T19:29:57.990Z</v>
+        <v>2026-07-20T14:21:37.858Z</v>
       </c>
     </row>
     <row r="5">
@@ -435,7 +433,7 @@
         <v>Row count</v>
       </c>
       <c r="B5">
-        <v>284</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -443,7 +441,7 @@
         <v>Sum debits / payments</v>
       </c>
       <c r="B6">
-        <v>419133070.67999965</v>
+        <v>419133588.17999965</v>
       </c>
     </row>
     <row r="7">
@@ -761,16 +759,16 @@
         <v>07/09/2023</v>
       </c>
       <c r="B25" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D25" t="str">
         <v>07/09/2023</v>
       </c>
       <c r="E25">
-        <v>2000000</v>
+        <v>4.5</v>
       </c>
       <c r="G25">
-        <v>-10487580.18</v>
+        <v>-8487580.18</v>
       </c>
     </row>
     <row r="26">
@@ -784,10 +782,10 @@
         <v>07/09/2023</v>
       </c>
       <c r="E26">
-        <v>13395.59</v>
+        <v>2000000</v>
       </c>
       <c r="G26">
-        <v>-10500980.27</v>
+        <v>-10487580.18</v>
       </c>
     </row>
     <row r="27">
@@ -795,16 +793,16 @@
         <v>07/09/2023</v>
       </c>
       <c r="B27" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D27" t="str">
         <v>07/09/2023</v>
       </c>
       <c r="E27">
-        <v>10182.18</v>
+        <v>4.5</v>
       </c>
       <c r="G27">
-        <v>-10511166.95</v>
+        <v>-10487584.68</v>
       </c>
     </row>
     <row r="28">
@@ -818,10 +816,10 @@
         <v>07/09/2023</v>
       </c>
       <c r="E28">
-        <v>367453.83</v>
+        <v>13395.59</v>
       </c>
       <c r="G28">
-        <v>-10878625.28</v>
+        <v>-10500980.27</v>
       </c>
     </row>
     <row r="29">
@@ -829,141 +827,141 @@
         <v>07/09/2023</v>
       </c>
       <c r="B29" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C29" t="str">
-        <v>/009SWI2191540006</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D29" t="str">
         <v>07/09/2023</v>
       </c>
-      <c r="F29">
-        <v>10879114.78</v>
+      <c r="E29">
+        <v>4.5</v>
       </c>
       <c r="G29">
-        <v>485</v>
+        <v>-10500984.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>11/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="B30" t="str">
-        <v>DIGITAL BANKING FEE</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D30" t="str">
-        <v>01/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>10182.18</v>
       </c>
       <c r="G30">
-        <v>470</v>
+        <v>-10511166.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>11/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="B31" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C31" t="str">
-        <v>/009SWI2191540006</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D31" t="str">
-        <v>11/09/2023</v>
-      </c>
-      <c r="F31">
-        <v>15</v>
+        <v>07/09/2023</v>
+      </c>
+      <c r="E31">
+        <v>4.5</v>
       </c>
       <c r="G31">
-        <v>485</v>
+        <v>-10511171.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>12/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="B32" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D32" t="str">
-        <v>12/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="E32">
-        <v>300</v>
+        <v>367453.83</v>
       </c>
       <c r="G32">
-        <v>185</v>
+        <v>-10878625.28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>12/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="B33" t="str">
         <v>COMMISSION</v>
       </c>
       <c r="D33" t="str">
-        <v>12/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="E33">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G33">
-        <v>181.5</v>
+        <v>-10878629.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>12/09/2023</v>
+        <v>07/09/2023</v>
       </c>
       <c r="B34" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C34" t="str">
+        <v>/009SWI2191540006</v>
       </c>
       <c r="D34" t="str">
-        <v>12/09/2023</v>
-      </c>
-      <c r="E34">
-        <v>877076.47</v>
+        <v>07/09/2023</v>
+      </c>
+      <c r="F34">
+        <v>10879114.78</v>
       </c>
       <c r="G34">
-        <v>-876894.97</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>12/09/2023</v>
+        <v>11/09/2023</v>
       </c>
       <c r="B35" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>DIGITAL BANKING FEE</v>
       </c>
       <c r="D35" t="str">
-        <v>12/09/2023</v>
+        <v>01/09/2023</v>
       </c>
       <c r="E35">
-        <v>400</v>
+        <v>15</v>
       </c>
       <c r="G35">
-        <v>-877299.47</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>12/09/2023</v>
+        <v>11/09/2023</v>
       </c>
       <c r="B36" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C36" t="str">
+        <v>/009SWI2191540006</v>
       </c>
       <c r="D36" t="str">
-        <v>12/09/2023</v>
-      </c>
-      <c r="E36">
-        <v>1000</v>
+        <v>11/09/2023</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
       </c>
       <c r="G36">
-        <v>-878303.47</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37">
@@ -977,10 +975,10 @@
         <v>12/09/2023</v>
       </c>
       <c r="E37">
-        <v>696150.52</v>
+        <v>300</v>
       </c>
       <c r="G37">
-        <v>-1574458.49</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38">
@@ -988,16 +986,16 @@
         <v>12/09/2023</v>
       </c>
       <c r="B38" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D38" t="str">
         <v>12/09/2023</v>
       </c>
       <c r="E38">
-        <v>831547.11</v>
+        <v>3.5</v>
       </c>
       <c r="G38">
-        <v>-2406010.1</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="39">
@@ -1011,10 +1009,10 @@
         <v>12/09/2023</v>
       </c>
       <c r="E39">
-        <v>500</v>
+        <v>877076.47</v>
       </c>
       <c r="G39">
-        <v>-2406514.6</v>
+        <v>-876894.97</v>
       </c>
     </row>
     <row r="40">
@@ -1022,19 +1020,16 @@
         <v>12/09/2023</v>
       </c>
       <c r="B40" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C40" t="str">
-        <v>/009SWI2191540006</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D40" t="str">
         <v>12/09/2023</v>
       </c>
-      <c r="F40">
-        <v>2595113.32</v>
+      <c r="E40">
+        <v>4.5</v>
       </c>
       <c r="G40">
-        <v>188594.22</v>
+        <v>-876899.47</v>
       </c>
     </row>
     <row r="41">
@@ -1048,10 +1043,10 @@
         <v>12/09/2023</v>
       </c>
       <c r="E41">
-        <v>29973.73</v>
+        <v>400</v>
       </c>
       <c r="G41">
-        <v>158620.49</v>
+        <v>-877299.47</v>
       </c>
     </row>
     <row r="42">
@@ -1059,16 +1054,16 @@
         <v>12/09/2023</v>
       </c>
       <c r="B42" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D42" t="str">
         <v>12/09/2023</v>
       </c>
       <c r="E42">
-        <v>157922.99</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>693</v>
+        <v>-877303.47</v>
       </c>
     </row>
     <row r="43">
@@ -1076,16 +1071,16 @@
         <v>12/09/2023</v>
       </c>
       <c r="B43" t="str">
-        <v>COMMISSION</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D43" t="str">
         <v>12/09/2023</v>
       </c>
       <c r="E43">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="G43">
-        <v>688.5</v>
+        <v>-878303.47</v>
       </c>
     </row>
     <row r="44">
@@ -1093,16 +1088,16 @@
         <v>12/09/2023</v>
       </c>
       <c r="B44" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D44" t="str">
         <v>12/09/2023</v>
       </c>
       <c r="E44">
-        <v>200</v>
+        <v>4.5</v>
       </c>
       <c r="G44">
-        <v>488.5</v>
+        <v>-878307.97</v>
       </c>
     </row>
     <row r="45">
@@ -1110,257 +1105,260 @@
         <v>12/09/2023</v>
       </c>
       <c r="B45" t="str">
-        <v>COMMISSION</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D45" t="str">
         <v>12/09/2023</v>
       </c>
       <c r="E45">
-        <v>3.5</v>
+        <v>696150.52</v>
       </c>
       <c r="G45">
-        <v>485</v>
+        <v>-1574458.49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>13/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B46" t="str">
-        <v>SWIFT TRANSFER - LOCAL</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D46" t="str">
-        <v>13/09/2023</v>
-      </c>
-      <c r="F46">
-        <v>110000000</v>
+        <v>12/09/2023</v>
+      </c>
+      <c r="E46">
+        <v>4.5</v>
       </c>
       <c r="G46">
-        <v>110000485</v>
+        <v>-1574462.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>13/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B47" t="str">
-        <v>CALL TRANSACTIONS - DR</v>
-      </c>
-      <c r="C47" t="str">
-        <v>/009SWO1191540006</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D47" t="str">
-        <v>13/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E47">
-        <v>109999300</v>
+        <v>831547.11</v>
       </c>
       <c r="G47">
-        <v>1185</v>
+        <v>-2406010.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B48" t="str">
-        <v>SWIFT TRANSFER - LOCAL</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D48" t="str">
-        <v>14/09/2023</v>
-      </c>
-      <c r="F48">
-        <v>27738097.48</v>
+        <v>12/09/2023</v>
+      </c>
+      <c r="E48">
+        <v>4.5</v>
       </c>
       <c r="G48">
-        <v>27739282.48</v>
+        <v>-2406014.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B49" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D49" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E49">
-        <v>7369624.88</v>
+        <v>500</v>
       </c>
       <c r="G49">
-        <v>20369657.6</v>
+        <v>-2406514.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B50" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D50" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E50">
-        <v>3674740.88</v>
+        <v>4.5</v>
       </c>
       <c r="G50">
-        <v>16694912.22</v>
+        <v>-2406519.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B51" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C51" t="str">
+        <v>/009SWI2191540006</v>
       </c>
       <c r="D51" t="str">
-        <v>14/09/2023</v>
-      </c>
-      <c r="E51">
-        <v>1361080.13</v>
+        <v>12/09/2023</v>
+      </c>
+      <c r="F51">
+        <v>2595113.32</v>
       </c>
       <c r="G51">
-        <v>15333827.59</v>
+        <v>188594.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B52" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D52" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E52">
-        <v>956677.61</v>
+        <v>29973.73</v>
       </c>
       <c r="G52">
-        <v>14377145.48</v>
+        <v>158620.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B53" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D53" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E53">
-        <v>3932412.81</v>
+        <v>4.5</v>
       </c>
       <c r="G53">
-        <v>10444728.17</v>
+        <v>158615.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B54" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D54" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E54">
-        <v>423080.12</v>
+        <v>157922.99</v>
       </c>
       <c r="G54">
-        <v>10021643.55</v>
+        <v>693</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B55" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D55" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E55">
-        <v>800395.48</v>
+        <v>4.5</v>
       </c>
       <c r="G55">
-        <v>9221243.57</v>
+        <v>688.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B56" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D56" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E56">
-        <v>1537303.36</v>
+        <v>200</v>
       </c>
       <c r="G56">
-        <v>7683935.71</v>
+        <v>488.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="B57" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D57" t="str">
-        <v>14/09/2023</v>
+        <v>12/09/2023</v>
       </c>
       <c r="E57">
-        <v>500719.89</v>
+        <v>3.5</v>
       </c>
       <c r="G57">
-        <v>7183211.32</v>
+        <v>485</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>14/09/2023</v>
+        <v>13/09/2023</v>
       </c>
       <c r="B58" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>SWIFT TRANSFER - LOCAL</v>
       </c>
       <c r="D58" t="str">
-        <v>14/09/2023</v>
-      </c>
-      <c r="E58">
-        <v>1710478.45</v>
+        <v>13/09/2023</v>
+      </c>
+      <c r="F58">
+        <v>110000000</v>
       </c>
       <c r="G58">
-        <v>5472728.37</v>
+        <v>110000485</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>14/09/2023</v>
+        <v>13/09/2023</v>
       </c>
       <c r="B59" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - DR</v>
+      </c>
+      <c r="C59" t="str">
+        <v>/009SWO1191540006</v>
       </c>
       <c r="D59" t="str">
-        <v>14/09/2023</v>
+        <v>13/09/2023</v>
       </c>
       <c r="E59">
-        <v>4900347.7</v>
+        <v>109999300</v>
       </c>
       <c r="G59">
-        <v>572376.17</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="60">
@@ -1368,16 +1366,16 @@
         <v>14/09/2023</v>
       </c>
       <c r="B60" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>SWIFT TRANSFER - LOCAL</v>
       </c>
       <c r="D60" t="str">
         <v>14/09/2023</v>
       </c>
-      <c r="E60">
-        <v>1199705.94</v>
+      <c r="F60">
+        <v>27738097.48</v>
       </c>
       <c r="G60">
-        <v>-627334.27</v>
+        <v>27739282.48</v>
       </c>
     </row>
     <row r="61">
@@ -1391,10 +1389,10 @@
         <v>14/09/2023</v>
       </c>
       <c r="E61">
-        <v>1109003.29</v>
+        <v>7369624.88</v>
       </c>
       <c r="G61">
-        <v>-1736342.06</v>
+        <v>20369657.6</v>
       </c>
     </row>
     <row r="62">
@@ -1402,16 +1400,16 @@
         <v>14/09/2023</v>
       </c>
       <c r="B62" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D62" t="str">
         <v>14/09/2023</v>
       </c>
       <c r="E62">
-        <v>42305.41</v>
+        <v>4.5</v>
       </c>
       <c r="G62">
-        <v>-1778651.97</v>
+        <v>20369653.1</v>
       </c>
     </row>
     <row r="63">
@@ -1425,10 +1423,10 @@
         <v>14/09/2023</v>
       </c>
       <c r="E63">
-        <v>1152406.72</v>
+        <v>3674740.88</v>
       </c>
       <c r="G63">
-        <v>-2931063.19</v>
+        <v>16694912.22</v>
       </c>
     </row>
     <row r="64">
@@ -1436,19 +1434,16 @@
         <v>14/09/2023</v>
       </c>
       <c r="B64" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C64" t="str">
-        <v>/009SWI2191540006</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D64" t="str">
         <v>14/09/2023</v>
       </c>
-      <c r="F64">
-        <v>18596210.11</v>
+      <c r="E64">
+        <v>4.5</v>
       </c>
       <c r="G64">
-        <v>15665142.42</v>
+        <v>16694907.72</v>
       </c>
     </row>
     <row r="65">
@@ -1462,10 +1457,10 @@
         <v>14/09/2023</v>
       </c>
       <c r="E65">
-        <v>6814496.75</v>
+        <v>1361080.13</v>
       </c>
       <c r="G65">
-        <v>8850645.67</v>
+        <v>15333827.59</v>
       </c>
     </row>
     <row r="66">
@@ -1473,16 +1468,16 @@
         <v>14/09/2023</v>
       </c>
       <c r="B66" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D66" t="str">
         <v>14/09/2023</v>
       </c>
       <c r="E66">
-        <v>6125005.35</v>
+        <v>4.5</v>
       </c>
       <c r="G66">
-        <v>2725635.82</v>
+        <v>15333823.09</v>
       </c>
     </row>
     <row r="67">
@@ -1496,10 +1491,10 @@
         <v>14/09/2023</v>
       </c>
       <c r="E67">
-        <v>1450420.11</v>
+        <v>956677.61</v>
       </c>
       <c r="G67">
-        <v>1275211.21</v>
+        <v>14377145.48</v>
       </c>
     </row>
     <row r="68">
@@ -1507,16 +1502,16 @@
         <v>14/09/2023</v>
       </c>
       <c r="B68" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D68" t="str">
         <v>14/09/2023</v>
       </c>
       <c r="E68">
-        <v>1274717.21</v>
+        <v>4.5</v>
       </c>
       <c r="G68">
-        <v>489.5</v>
+        <v>14377140.98</v>
       </c>
     </row>
     <row r="69">
@@ -1524,529 +1519,529 @@
         <v>14/09/2023</v>
       </c>
       <c r="B69" t="str">
-        <v>COMMISSION</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D69" t="str">
         <v>14/09/2023</v>
       </c>
       <c r="E69">
-        <v>4.5</v>
+        <v>3932412.81</v>
       </c>
       <c r="G69">
-        <v>485</v>
+        <v>10444728.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B70" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D70" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E70">
-        <v>436595.15</v>
+        <v>4.5</v>
       </c>
       <c r="G70">
-        <v>-436110.15</v>
+        <v>10444723.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B71" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D71" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E71">
-        <v>200</v>
+        <v>423080.12</v>
       </c>
       <c r="G71">
-        <v>-436310.15</v>
+        <v>10021643.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B72" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D72" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E72">
-        <v>373772.5</v>
+        <v>4.5</v>
       </c>
       <c r="G72">
-        <v>-810082.65</v>
+        <v>10021639.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B73" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D73" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E73">
-        <v>125329</v>
+        <v>800395.48</v>
       </c>
       <c r="G73">
-        <v>-935411.65</v>
+        <v>9221243.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B74" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D74" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E74">
-        <v>168488.75</v>
+        <v>4.5</v>
       </c>
       <c r="G74">
-        <v>-1103900.4</v>
+        <v>9221239.07</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B75" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D75" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E75">
-        <v>421762.49</v>
+        <v>1537303.36</v>
       </c>
       <c r="G75">
-        <v>-1525662.89</v>
+        <v>7683935.71</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B76" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D76" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E76">
-        <v>515643.6</v>
+        <v>4.5</v>
       </c>
       <c r="G76">
-        <v>-2041306.49</v>
+        <v>7683931.21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B77" t="str">
-        <v>DEBIT TRANSFER</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D77" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E77">
-        <v>190</v>
+        <v>500719.89</v>
       </c>
       <c r="G77">
-        <v>-2041496.49</v>
+        <v>7183211.32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B78" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D78" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E78">
-        <v>300431.93</v>
+        <v>4.5</v>
       </c>
       <c r="G78">
-        <v>-2341928.42</v>
+        <v>7183206.82</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B79" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D79" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E79">
-        <v>855000</v>
+        <v>1710478.45</v>
       </c>
       <c r="G79">
-        <v>-3196928.42</v>
+        <v>5472728.37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B80" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D80" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E80">
-        <v>200287.96</v>
+        <v>4.5</v>
       </c>
       <c r="G80">
-        <v>-3397216.38</v>
+        <v>5472723.87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B81" t="str">
-        <v>INWARD CLEARING : ENTERPRISE INSURANCE CO LTD</v>
-      </c>
-      <c r="C81" t="str">
-        <v>/0096744232580001</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D81" t="str">
-        <v>15/09/2023</v>
-      </c>
-      <c r="F81">
-        <v>91021.55</v>
+        <v>14/09/2023</v>
+      </c>
+      <c r="E81">
+        <v>4900347.7</v>
       </c>
       <c r="G81">
-        <v>-3488237.93</v>
+        <v>572376.17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B82" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D82" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E82">
-        <v>1313635.37</v>
+        <v>4.5</v>
       </c>
       <c r="G82">
-        <v>-4801873.3</v>
+        <v>572371.67</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B83" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D83" t="str">
-        <v>15/09/2023</v>
-      </c>
-      <c r="F83">
-        <v>351241.25</v>
+        <v>14/09/2023</v>
+      </c>
+      <c r="E83">
+        <v>1199705.94</v>
       </c>
       <c r="G83">
-        <v>-5153114.55</v>
+        <v>-627334.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B84" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D84" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E84">
-        <v>3781212.31</v>
+        <v>4.5</v>
       </c>
       <c r="G84">
-        <v>-8934326.86</v>
+        <v>-627338.77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B85" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D85" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E85">
-        <v>13635745.99</v>
+        <v>1109003.29</v>
       </c>
       <c r="G85">
-        <v>-22570072.85</v>
+        <v>-1736342.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B86" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D86" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E86">
-        <v>1114592.69</v>
+        <v>4.5</v>
       </c>
       <c r="G86">
-        <v>-23684665.54</v>
+        <v>-1736346.56</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B87" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D87" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E87">
-        <v>1026049.58</v>
+        <v>42305.41</v>
       </c>
       <c r="G87">
-        <v>-24710715.12</v>
+        <v>-1778651.97</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B88" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D88" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E88">
-        <v>21623921.07</v>
+        <v>4.5</v>
       </c>
       <c r="G88">
-        <v>-46334636.19</v>
+        <v>-1778656.47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B89" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D89" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E89">
-        <v>2436202.86</v>
+        <v>1152406.72</v>
       </c>
       <c r="G89">
-        <v>-48770839.05</v>
+        <v>-2931063.19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B90" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D90" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E90">
-        <v>2294963.31</v>
+        <v>4.5</v>
       </c>
       <c r="G90">
-        <v>-51065802.36</v>
+        <v>-2931067.69</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B91" t="str">
-        <v>OUTGOING RT ACH</v>
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C91" t="str">
+        <v>/009SWI2191540006</v>
       </c>
       <c r="D91" t="str">
-        <v>15/09/2023</v>
-      </c>
-      <c r="E91">
-        <v>1387211.84</v>
+        <v>14/09/2023</v>
+      </c>
+      <c r="F91">
+        <v>18596210.11</v>
       </c>
       <c r="G91">
-        <v>-52453014.2</v>
+        <v>15665142.42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B92" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D92" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E92">
-        <v>314683.03</v>
+        <v>6814496.75</v>
       </c>
       <c r="G92">
-        <v>-52767697.23</v>
+        <v>8850645.67</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B93" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D93" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E93">
-        <v>1796.78</v>
+        <v>4.5</v>
       </c>
       <c r="G93">
-        <v>-52769498.51</v>
+        <v>8850641.17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B94" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D94" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E94">
-        <v>40448.4</v>
+        <v>6125005.35</v>
       </c>
       <c r="G94">
-        <v>-52809951.41</v>
+        <v>2725635.82</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B95" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D95" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E95">
-        <v>8827.05</v>
+        <v>4.5</v>
       </c>
       <c r="G95">
-        <v>-52818782.96</v>
+        <v>2725631.32</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B96" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D96" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E96">
-        <v>122332.54</v>
+        <v>1450420.11</v>
       </c>
       <c r="G96">
-        <v>-52941120</v>
+        <v>1275211.21</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B97" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D97" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E97">
-        <v>2900912.58</v>
+        <v>4.5</v>
       </c>
       <c r="G97">
-        <v>-55842037.08</v>
+        <v>1275206.71</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B98" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D98" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E98">
-        <v>371802.56</v>
+        <v>1274717.21</v>
       </c>
       <c r="G98">
-        <v>-56213844.14</v>
+        <v>489.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="B99" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D99" t="str">
-        <v>15/09/2023</v>
+        <v>14/09/2023</v>
       </c>
       <c r="E99">
-        <v>10000</v>
+        <v>4.5</v>
       </c>
       <c r="G99">
-        <v>-56223848.64</v>
+        <v>485</v>
       </c>
     </row>
     <row r="100">
@@ -2054,16 +2049,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B100" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D100" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E100">
-        <v>100</v>
+        <v>436595.15</v>
       </c>
       <c r="G100">
-        <v>-56223953.14</v>
+        <v>-436110.15</v>
       </c>
     </row>
     <row r="101">
@@ -2071,16 +2066,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B101" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D101" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E101">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G101">
-        <v>-56224056.64</v>
+        <v>-436310.15</v>
       </c>
     </row>
     <row r="102">
@@ -2088,16 +2083,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B102" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D102" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E102">
-        <v>30232.02</v>
+        <v>373772.5</v>
       </c>
       <c r="G102">
-        <v>-56254292.16</v>
+        <v>-810082.65</v>
       </c>
     </row>
     <row r="103">
@@ -2105,16 +2100,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B103" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D103" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E103">
-        <v>200</v>
+        <v>125329</v>
       </c>
       <c r="G103">
-        <v>-56254496.66</v>
+        <v>-935411.65</v>
       </c>
     </row>
     <row r="104">
@@ -2122,16 +2117,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B104" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D104" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E104">
-        <v>45450</v>
+        <v>168488.75</v>
       </c>
       <c r="G104">
-        <v>-56299950.16</v>
+        <v>-1103900.4</v>
       </c>
     </row>
     <row r="105">
@@ -2139,16 +2134,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B105" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D105" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E105">
-        <v>346988.08</v>
+        <v>421762.49</v>
       </c>
       <c r="G105">
-        <v>-56646942.74</v>
+        <v>-1525662.89</v>
       </c>
     </row>
     <row r="106">
@@ -2156,16 +2151,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B106" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D106" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E106">
-        <v>347715.72</v>
+        <v>515643.6</v>
       </c>
       <c r="G106">
-        <v>-56994662.96</v>
+        <v>-2041306.49</v>
       </c>
     </row>
     <row r="107">
@@ -2173,16 +2168,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B107" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>DEBIT TRANSFER</v>
       </c>
       <c r="D107" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E107">
-        <v>597099.32</v>
+        <v>190</v>
       </c>
       <c r="G107">
-        <v>-57591766.78</v>
+        <v>-2041496.49</v>
       </c>
     </row>
     <row r="108">
@@ -2190,16 +2185,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B108" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D108" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E108">
-        <v>2563053.04</v>
+        <v>300431.93</v>
       </c>
       <c r="G108">
-        <v>-60154824.32</v>
+        <v>-2341928.42</v>
       </c>
     </row>
     <row r="109">
@@ -2207,16 +2202,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B109" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D109" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E109">
-        <v>69679.9</v>
+        <v>855000</v>
       </c>
       <c r="G109">
-        <v>-60224508.72</v>
+        <v>-3196928.42</v>
       </c>
     </row>
     <row r="110">
@@ -2224,16 +2219,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B110" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D110" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E110">
-        <v>178312.13</v>
+        <v>200287.96</v>
       </c>
       <c r="G110">
-        <v>-60402825.35</v>
+        <v>-3397216.38</v>
       </c>
     </row>
     <row r="111">
@@ -2241,16 +2236,19 @@
         <v>15/09/2023</v>
       </c>
       <c r="B111" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING : ENTERPRISE INSURANCE CO LTD</v>
+      </c>
+      <c r="C111" t="str">
+        <v>/0096744232580001</v>
       </c>
       <c r="D111" t="str">
         <v>15/09/2023</v>
       </c>
-      <c r="E111">
-        <v>490363.01</v>
+      <c r="F111">
+        <v>91021.55</v>
       </c>
       <c r="G111">
-        <v>-60893192.86</v>
+        <v>-3488237.93</v>
       </c>
     </row>
     <row r="112">
@@ -2258,16 +2256,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B112" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D112" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E112">
-        <v>634165.13</v>
+        <v>1313635.37</v>
       </c>
       <c r="G112">
-        <v>-61527362.49</v>
+        <v>-4801873.3</v>
       </c>
     </row>
     <row r="113">
@@ -2275,16 +2273,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B113" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D113" t="str">
         <v>15/09/2023</v>
       </c>
-      <c r="E113">
-        <v>133135.7</v>
+      <c r="F113">
+        <v>351241.25</v>
       </c>
       <c r="G113">
-        <v>-61660502.69</v>
+        <v>-5153114.55</v>
       </c>
     </row>
     <row r="114">
@@ -2292,16 +2290,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B114" t="str">
-        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D114" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E114">
-        <v>35552</v>
+        <v>3781212.31</v>
       </c>
       <c r="G114">
-        <v>-61696059.19</v>
+        <v>-8934326.86</v>
       </c>
     </row>
     <row r="115">
@@ -2309,19 +2307,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B115" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C115" t="str">
-        <v>/009SWI2191540006</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D115" t="str">
         <v>15/09/2023</v>
       </c>
-      <c r="F115">
-        <v>62064542.06</v>
+      <c r="E115">
+        <v>13635745.99</v>
       </c>
       <c r="G115">
-        <v>368482.87</v>
+        <v>-22570072.85</v>
       </c>
     </row>
     <row r="116">
@@ -2329,16 +2324,16 @@
         <v>15/09/2023</v>
       </c>
       <c r="B116" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D116" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E116">
-        <v>367993.37</v>
+        <v>1114592.69</v>
       </c>
       <c r="G116">
-        <v>489.5</v>
+        <v>-23684665.54</v>
       </c>
     </row>
     <row r="117">
@@ -2346,1088 +2341,1079 @@
         <v>15/09/2023</v>
       </c>
       <c r="B117" t="str">
-        <v>COMMISSION</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D117" t="str">
         <v>15/09/2023</v>
       </c>
       <c r="E117">
-        <v>4.5</v>
+        <v>1026049.58</v>
       </c>
       <c r="G117">
-        <v>485</v>
+        <v>-24710715.12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>18/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B118" t="str">
-        <v>SWIFT TRANSFER - LOCAL</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D118" t="str">
-        <v>18/09/2023</v>
-      </c>
-      <c r="F118">
-        <v>32683288.26</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E118">
+        <v>21623921.07</v>
       </c>
       <c r="G118">
-        <v>32683773.26</v>
+        <v>-46334636.19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>18/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B119" t="str">
-        <v>SWIFT TRANSFER - LOCAL</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D119" t="str">
-        <v>18/09/2023</v>
-      </c>
-      <c r="F119">
-        <v>3500000</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E119">
+        <v>2436202.86</v>
       </c>
       <c r="G119">
-        <v>36183773.26</v>
+        <v>-48770839.05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>18/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B120" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D120" t="str">
-        <v>18/09/2023</v>
-      </c>
-      <c r="F120">
-        <v>150000</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E120">
+        <v>2294963.31</v>
       </c>
       <c r="G120">
-        <v>36033773.26</v>
+        <v>-51065802.36</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>18/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B121" t="str">
-        <v>CALL TRANSACTIONS - DR</v>
-      </c>
-      <c r="C121" t="str">
-        <v>/009SWO1191540006</v>
+        <v>OUTGOING RT ACH</v>
       </c>
       <c r="D121" t="str">
-        <v>18/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E121">
-        <v>36032588.26</v>
+        <v>1387211.84</v>
       </c>
       <c r="G121">
-        <v>1185</v>
+        <v>-52453014.2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B122" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D122" t="str">
-        <v>19/09/2023</v>
-      </c>
-      <c r="F122">
-        <v>310694.42</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E122">
+        <v>314683.03</v>
       </c>
       <c r="G122">
-        <v>-309509.42</v>
+        <v>-52767697.23</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B123" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D123" t="str">
-        <v>19/09/2023</v>
-      </c>
-      <c r="F123">
-        <v>506088.64</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E123">
+        <v>4.5</v>
       </c>
       <c r="G123">
-        <v>-815598.06</v>
+        <v>-52767701.73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B124" t="str">
-        <v>SWIFT TRANSFER - LOCAL</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D124" t="str">
-        <v>19/09/2023</v>
-      </c>
-      <c r="F124">
-        <v>25000000</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E124">
+        <v>1796.78</v>
       </c>
       <c r="G124">
-        <v>24184401.94</v>
+        <v>-52769498.51</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B125" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D125" t="str">
-        <v>19/09/2023</v>
-      </c>
-      <c r="F125">
-        <v>88611.25</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E125">
+        <v>4.5</v>
       </c>
       <c r="G125">
-        <v>24095790.69</v>
+        <v>-52769503.01</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B126" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D126" t="str">
-        <v>19/09/2023</v>
-      </c>
-      <c r="F126">
-        <v>95950</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E126">
+        <v>40448.4</v>
       </c>
       <c r="G126">
-        <v>23999840.69</v>
+        <v>-52809951.41</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B127" t="str">
-        <v>CALL TRANSACTIONS - DR</v>
-      </c>
-      <c r="C127" t="str">
-        <v>/009SWO1191540006</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D127" t="str">
-        <v>19/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E127">
-        <v>23998655.69</v>
+        <v>4.5</v>
       </c>
       <c r="G127">
-        <v>1185</v>
+        <v>-52809955.91</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B128" t="str">
-        <v>INWARD CLEARING : HILDA AND HILDA LTD</v>
-      </c>
-      <c r="C128" t="str">
-        <v>/0096948232630001</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D128" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F128">
-        <v>91910</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E128">
+        <v>8827.05</v>
       </c>
       <c r="G128">
-        <v>-90725</v>
+        <v>-52818782.96</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B129" t="str">
-        <v>INWARD CLEARING : FOCAL INTEGRITY LOGISTICS LTD</v>
-      </c>
-      <c r="C129" t="str">
-        <v>/0096263232630001</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D129" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F129">
-        <v>88880</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E129">
+        <v>4.5</v>
       </c>
       <c r="G129">
-        <v>-179605</v>
+        <v>-52818787.46</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B130" t="str">
-        <v>INWARD CLEARING : APPLIANCE POINT</v>
-      </c>
-      <c r="C130" t="str">
-        <v>/0096263232630003</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D130" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F130">
-        <v>51878.65</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E130">
+        <v>122332.54</v>
       </c>
       <c r="G130">
-        <v>-231483.65</v>
+        <v>-52941120</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B131" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D131" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F131">
-        <v>305664.57</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E131">
+        <v>4.5</v>
       </c>
       <c r="G131">
-        <v>-537148.22</v>
+        <v>-52941124.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B132" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D132" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F132">
-        <v>70700</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E132">
+        <v>2900912.58</v>
       </c>
       <c r="G132">
-        <v>-607848.22</v>
+        <v>-55842037.08</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B133" t="str">
-        <v>DEBIT TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D133" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E133">
-        <v>61278.26</v>
+        <v>4.5</v>
       </c>
       <c r="G133">
-        <v>-669126.48</v>
+        <v>-55842041.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B134" t="str">
-        <v>COMMISSION</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D134" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E134">
-        <v>100</v>
+        <v>371802.56</v>
       </c>
       <c r="G134">
-        <v>-669226.48</v>
+        <v>-56213844.14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B135" t="str">
-        <v>DEBIT TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D135" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E135">
-        <v>1839.31</v>
+        <v>4.5</v>
       </c>
       <c r="G135">
-        <v>-671065.79</v>
+        <v>-56213848.64</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B136" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D136" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F136">
-        <v>71411.8</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E136">
+        <v>10000</v>
       </c>
       <c r="G136">
-        <v>-742477.59</v>
+        <v>-56223848.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B137" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D137" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="F137">
-        <v>39703.1</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="E137">
+        <v>4.5</v>
       </c>
       <c r="G137">
-        <v>-782180.69</v>
+        <v>-56223853.14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B138" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D138" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E138">
-        <v>18430.22</v>
+        <v>100</v>
       </c>
       <c r="G138">
-        <v>-800610.91</v>
+        <v>-56223953.14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B139" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D139" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E139">
-        <v>2259191.06</v>
+        <v>3.5</v>
       </c>
       <c r="G139">
-        <v>-3059806.47</v>
+        <v>-56223956.64</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B140" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D140" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E140">
-        <v>23605.14</v>
+        <v>100</v>
       </c>
       <c r="G140">
-        <v>-3083416.11</v>
+        <v>-56224056.64</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B141" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D141" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E141">
-        <v>15978.2</v>
+        <v>3.5</v>
       </c>
       <c r="G141">
-        <v>-3099398.81</v>
+        <v>-56224060.14</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B142" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D142" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E142">
-        <v>2239345.77</v>
+        <v>30232.02</v>
       </c>
       <c r="G142">
-        <v>-5338749.08</v>
+        <v>-56254292.16</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B143" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D143" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E143">
-        <v>23634</v>
+        <v>4.5</v>
       </c>
       <c r="G143">
-        <v>-5362387.58</v>
+        <v>-56254296.66</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B144" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D144" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E144">
-        <v>10212.22</v>
+        <v>200</v>
       </c>
       <c r="G144">
-        <v>-5372604.3</v>
+        <v>-56254496.66</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B145" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D145" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E145">
-        <v>1476065.7</v>
+        <v>3.5</v>
       </c>
       <c r="G145">
-        <v>-6848674.5</v>
+        <v>-56254500.16</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B146" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D146" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E146">
-        <v>4590.5</v>
+        <v>45450</v>
       </c>
       <c r="G146">
-        <v>-6853269.5</v>
+        <v>-56299950.16</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B147" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D147" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E147">
-        <v>13049.2</v>
+        <v>4.5</v>
       </c>
       <c r="G147">
-        <v>-6866323.2</v>
+        <v>-56299954.66</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B148" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D148" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E148">
-        <v>10967.54</v>
+        <v>346988.08</v>
       </c>
       <c r="G148">
-        <v>-6877295.24</v>
+        <v>-56646942.74</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B149" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D149" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E149">
-        <v>3854907.24</v>
+        <v>4.5</v>
       </c>
       <c r="G149">
-        <v>-10732206.98</v>
+        <v>-56646947.24</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B150" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D150" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E150">
-        <v>44632.73</v>
+        <v>347715.72</v>
       </c>
       <c r="G150">
-        <v>-10776844.21</v>
+        <v>-56994662.96</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B151" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D151" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E151">
-        <v>2413500.59</v>
+        <v>4.5</v>
       </c>
       <c r="G151">
-        <v>-13190349.3</v>
+        <v>-56994667.46</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B152" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D152" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E152">
-        <v>2594.26</v>
+        <v>597099.32</v>
       </c>
       <c r="G152">
-        <v>-13192948.06</v>
+        <v>-57591766.78</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B153" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D153" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E153">
-        <v>2804.76</v>
+        <v>4.5</v>
       </c>
       <c r="G153">
-        <v>-13195757.32</v>
+        <v>-57591771.28</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B154" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D154" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E154">
-        <v>1339.42</v>
+        <v>2563053.04</v>
       </c>
       <c r="G154">
-        <v>-13197101.24</v>
+        <v>-60154824.32</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B155" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D155" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E155">
-        <v>7756.05</v>
+        <v>4.5</v>
       </c>
       <c r="G155">
-        <v>-13204861.79</v>
+        <v>-60154828.82</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B156" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D156" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E156">
-        <v>6353.64</v>
+        <v>69679.9</v>
       </c>
       <c r="G156">
-        <v>-13211219.93</v>
+        <v>-60224508.72</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B157" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D157" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E157">
-        <v>10013.5</v>
+        <v>4.5</v>
       </c>
       <c r="G157">
-        <v>-13221237.93</v>
+        <v>-60224513.22</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B158" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D158" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E158">
-        <v>28880</v>
+        <v>178312.13</v>
       </c>
       <c r="G158">
-        <v>-13250122.43</v>
+        <v>-60402825.35</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B159" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D159" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E159">
-        <v>35653</v>
+        <v>4.5</v>
       </c>
       <c r="G159">
-        <v>-13285779.93</v>
+        <v>-60402829.85</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B160" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D160" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E160">
-        <v>4544.86</v>
+        <v>490363.01</v>
       </c>
       <c r="G160">
-        <v>-13290329.29</v>
+        <v>-60893192.86</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B161" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D161" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E161">
-        <v>48493.8</v>
+        <v>4.5</v>
       </c>
       <c r="G161">
-        <v>-13338827.59</v>
+        <v>-60893197.36</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B162" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D162" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E162">
-        <v>2421993.4</v>
+        <v>634165.13</v>
       </c>
       <c r="G162">
-        <v>-15760825.49</v>
+        <v>-61527362.49</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B163" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D163" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E163">
-        <v>15142.85</v>
+        <v>4.5</v>
       </c>
       <c r="G163">
-        <v>-15775972.84</v>
+        <v>-61527366.99</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B164" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D164" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E164">
-        <v>4787.35</v>
+        <v>133135.7</v>
       </c>
       <c r="G164">
-        <v>-15780764.69</v>
+        <v>-61660502.69</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B165" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D165" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E165">
-        <v>3474.47</v>
+        <v>4.5</v>
       </c>
       <c r="G165">
-        <v>-15784243.66</v>
+        <v>-61660507.19</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B166" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
       </c>
       <c r="D166" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E166">
-        <v>25980.97</v>
+        <v>35552</v>
       </c>
       <c r="G166">
-        <v>-15810229.13</v>
+        <v>-61696059.19</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B167" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C167" t="str">
+        <v>/009SWI2191540006</v>
       </c>
       <c r="D167" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E167">
-        <v>8558.4</v>
+        <v>15/09/2023</v>
+      </c>
+      <c r="F167">
+        <v>62064542.06</v>
       </c>
       <c r="G167">
-        <v>-15818792.03</v>
+        <v>368482.87</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B168" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D168" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E168">
-        <v>2687158.38</v>
+        <v>367993.37</v>
       </c>
       <c r="G168">
-        <v>-18505954.91</v>
+        <v>489.5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="B169" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D169" t="str">
-        <v>20/09/2023</v>
+        <v>15/09/2023</v>
       </c>
       <c r="E169">
-        <v>4041.14</v>
+        <v>4.5</v>
       </c>
       <c r="G169">
-        <v>-18510000.55</v>
+        <v>485</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>20/09/2023</v>
+        <v>18/09/2023</v>
       </c>
       <c r="B170" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>SWIFT TRANSFER - LOCAL</v>
       </c>
       <c r="D170" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E170">
-        <v>8104.58</v>
+        <v>18/09/2023</v>
+      </c>
+      <c r="F170">
+        <v>32683288.26</v>
       </c>
       <c r="G170">
-        <v>-18518109.63</v>
+        <v>32683773.26</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>20/09/2023</v>
+        <v>18/09/2023</v>
       </c>
       <c r="B171" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>SWIFT TRANSFER - LOCAL</v>
       </c>
       <c r="D171" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E171">
-        <v>12328.5</v>
+        <v>18/09/2023</v>
+      </c>
+      <c r="F171">
+        <v>3500000</v>
       </c>
       <c r="G171">
-        <v>-18530442.63</v>
+        <v>36183773.26</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>20/09/2023</v>
+        <v>18/09/2023</v>
       </c>
       <c r="B172" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D172" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E172">
-        <v>1796447.76</v>
+        <v>18/09/2023</v>
+      </c>
+      <c r="F172">
+        <v>150000</v>
       </c>
       <c r="G172">
-        <v>-20326894.89</v>
+        <v>36033773.26</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>20/09/2023</v>
+        <v>18/09/2023</v>
       </c>
       <c r="B173" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - DR</v>
+      </c>
+      <c r="C173" t="str">
+        <v>/009SWO1191540006</v>
       </c>
       <c r="D173" t="str">
-        <v>20/09/2023</v>
+        <v>18/09/2023</v>
       </c>
       <c r="E173">
-        <v>5605.5</v>
+        <v>36032588.26</v>
       </c>
       <c r="G173">
-        <v>-20332504.89</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="B174" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D174" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E174">
-        <v>4129.43</v>
+        <v>19/09/2023</v>
+      </c>
+      <c r="F174">
+        <v>310694.42</v>
       </c>
       <c r="G174">
-        <v>-20336638.82</v>
+        <v>-309509.42</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="B175" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D175" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E175">
-        <v>9998.69</v>
+        <v>19/09/2023</v>
+      </c>
+      <c r="F175">
+        <v>506088.64</v>
       </c>
       <c r="G175">
-        <v>-20346642.01</v>
+        <v>-815598.06</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="B176" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C176" t="str">
-        <v>/009SWI2191540006</v>
+        <v>SWIFT TRANSFER - LOCAL</v>
       </c>
       <c r="D176" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="F176">
-        <v>22480302.81</v>
+        <v>25000000</v>
       </c>
       <c r="G176">
-        <v>2133656.3</v>
+        <v>24184401.94</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="B177" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D177" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E177">
-        <v>2776.14</v>
+        <v>19/09/2023</v>
+      </c>
+      <c r="F177">
+        <v>88611.25</v>
       </c>
       <c r="G177">
-        <v>2130880.16</v>
+        <v>24095790.69</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="B178" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D178" t="str">
-        <v>20/09/2023</v>
-      </c>
-      <c r="E178">
-        <v>3530.34</v>
+        <v>19/09/2023</v>
+      </c>
+      <c r="F178">
+        <v>95950</v>
       </c>
       <c r="G178">
-        <v>2127345.32</v>
+        <v>23999840.69</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="B179" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>CALL TRANSACTIONS - DR</v>
+      </c>
+      <c r="C179" t="str">
+        <v>/009SWO1191540006</v>
       </c>
       <c r="D179" t="str">
-        <v>20/09/2023</v>
+        <v>19/09/2023</v>
       </c>
       <c r="E179">
-        <v>2203.79</v>
+        <v>23998655.69</v>
       </c>
       <c r="G179">
-        <v>2125137.03</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="180">
@@ -3435,16 +3421,19 @@
         <v>20/09/2023</v>
       </c>
       <c r="B180" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING : HILDA AND HILDA LTD</v>
+      </c>
+      <c r="C180" t="str">
+        <v>/0096948232630001</v>
       </c>
       <c r="D180" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E180">
-        <v>76138.46</v>
+      <c r="F180">
+        <v>91910</v>
       </c>
       <c r="G180">
-        <v>2048994.07</v>
+        <v>-90725</v>
       </c>
     </row>
     <row r="181">
@@ -3452,16 +3441,19 @@
         <v>20/09/2023</v>
       </c>
       <c r="B181" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING : FOCAL INTEGRITY LOGISTICS LTD</v>
+      </c>
+      <c r="C181" t="str">
+        <v>/0096263232630001</v>
       </c>
       <c r="D181" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E181">
-        <v>3863.7</v>
+      <c r="F181">
+        <v>88880</v>
       </c>
       <c r="G181">
-        <v>2045125.87</v>
+        <v>-179605</v>
       </c>
     </row>
     <row r="182">
@@ -3469,16 +3461,19 @@
         <v>20/09/2023</v>
       </c>
       <c r="B182" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING : APPLIANCE POINT</v>
+      </c>
+      <c r="C182" t="str">
+        <v>/0096263232630003</v>
       </c>
       <c r="D182" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E182">
-        <v>1999804.36</v>
+      <c r="F182">
+        <v>51878.65</v>
       </c>
       <c r="G182">
-        <v>45317.01</v>
+        <v>-231483.65</v>
       </c>
     </row>
     <row r="183">
@@ -3486,16 +3481,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B183" t="str">
-        <v>COMMISSION</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D183" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E183">
-        <v>4.5</v>
+      <c r="F183">
+        <v>305664.57</v>
       </c>
       <c r="G183">
-        <v>45312.51</v>
+        <v>-537148.22</v>
       </c>
     </row>
     <row r="184">
@@ -3503,16 +3498,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B184" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D184" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E184">
-        <v>5807.5</v>
+      <c r="F184">
+        <v>70700</v>
       </c>
       <c r="G184">
-        <v>39505.01</v>
+        <v>-607848.22</v>
       </c>
     </row>
     <row r="185">
@@ -3520,16 +3515,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B185" t="str">
-        <v>COMMISSION</v>
+        <v>DEBIT TRANSFER</v>
       </c>
       <c r="D185" t="str">
         <v>20/09/2023</v>
       </c>
       <c r="E185">
-        <v>4.5</v>
+        <v>61278.26</v>
       </c>
       <c r="G185">
-        <v>39500.51</v>
+        <v>-669126.48</v>
       </c>
     </row>
     <row r="186">
@@ -3537,16 +3532,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B186" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D186" t="str">
         <v>20/09/2023</v>
       </c>
       <c r="E186">
-        <v>5568.31</v>
+        <v>100</v>
       </c>
       <c r="G186">
-        <v>33932.2</v>
+        <v>-669226.48</v>
       </c>
     </row>
     <row r="187">
@@ -3554,16 +3549,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B187" t="str">
-        <v>COMMISSION</v>
+        <v>DEBIT TRANSFER</v>
       </c>
       <c r="D187" t="str">
         <v>20/09/2023</v>
       </c>
       <c r="E187">
-        <v>4.5</v>
+        <v>1839.31</v>
       </c>
       <c r="G187">
-        <v>33927.7</v>
+        <v>-671065.79</v>
       </c>
     </row>
     <row r="188">
@@ -3571,16 +3566,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B188" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D188" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E188">
-        <v>6424.15</v>
+      <c r="F188">
+        <v>71411.8</v>
       </c>
       <c r="G188">
-        <v>27503.55</v>
+        <v>-742477.59</v>
       </c>
     </row>
     <row r="189">
@@ -3588,16 +3583,16 @@
         <v>20/09/2023</v>
       </c>
       <c r="B189" t="str">
-        <v>COMMISSION</v>
+        <v>INWARD CLEARING EXPRESS</v>
       </c>
       <c r="D189" t="str">
         <v>20/09/2023</v>
       </c>
-      <c r="E189">
-        <v>4.5</v>
+      <c r="F189">
+        <v>39703.1</v>
       </c>
       <c r="G189">
-        <v>27499.05</v>
+        <v>-782180.69</v>
       </c>
     </row>
     <row r="190">
@@ -3611,10 +3606,10 @@
         <v>20/09/2023</v>
       </c>
       <c r="E190">
-        <v>16453.35</v>
+        <v>18430.22</v>
       </c>
       <c r="G190">
-        <v>11045.7</v>
+        <v>-800610.91</v>
       </c>
     </row>
     <row r="191">
@@ -3631,7 +3626,7 @@
         <v>4.5</v>
       </c>
       <c r="G191">
-        <v>11041.2</v>
+        <v>-800615.41</v>
       </c>
     </row>
     <row r="192">
@@ -3645,10 +3640,10 @@
         <v>20/09/2023</v>
       </c>
       <c r="E192">
-        <v>10551.7</v>
+        <v>2259191.06</v>
       </c>
       <c r="G192">
-        <v>489.5</v>
+        <v>-3059806.47</v>
       </c>
     </row>
     <row r="193">
@@ -3665,1751 +3660,3726 @@
         <v>4.5</v>
       </c>
       <c r="G193">
-        <v>485</v>
+        <v>-3059810.97</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B194" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D194" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E194">
-        <v>1717</v>
+        <v>23605.14</v>
       </c>
       <c r="G194">
-        <v>-1232</v>
+        <v>-3083416.11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B195" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D195" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E195">
-        <v>2727</v>
+        <v>4.5</v>
       </c>
       <c r="G195">
-        <v>-3959</v>
+        <v>-3083420.61</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B196" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D196" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E196">
-        <v>5959.01</v>
+        <v>15978.2</v>
       </c>
       <c r="G196">
-        <v>-9918.01</v>
+        <v>-3099398.81</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B197" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D197" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E197">
-        <v>4721.88</v>
+        <v>4.5</v>
       </c>
       <c r="G197">
-        <v>-14639.89</v>
+        <v>-3099403.31</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B198" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D198" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E198">
-        <v>11647.82</v>
+        <v>2239345.77</v>
       </c>
       <c r="G198">
-        <v>-26287.71</v>
+        <v>-5338749.08</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B199" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D199" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E199">
-        <v>8162.79</v>
+        <v>4.5</v>
       </c>
       <c r="G199">
-        <v>-34450.5</v>
+        <v>-5338753.58</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B200" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D200" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E200">
-        <v>5731.08</v>
+        <v>23634</v>
       </c>
       <c r="G200">
-        <v>-40181.58</v>
+        <v>-5362387.58</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B201" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D201" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E201">
-        <v>3048.93</v>
+        <v>4.5</v>
       </c>
       <c r="G201">
-        <v>-43230.51</v>
+        <v>-5362392.08</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B202" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D202" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E202">
-        <v>24835.34</v>
+        <v>10212.22</v>
       </c>
       <c r="G202">
-        <v>-68065.85</v>
+        <v>-5372604.3</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B203" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D203" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E203">
-        <v>43219.92</v>
+        <v>4.5</v>
       </c>
       <c r="G203">
-        <v>-111285.77</v>
+        <v>-5372608.8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B204" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D204" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E204">
-        <v>2040.2</v>
+        <v>1476065.7</v>
       </c>
       <c r="G204">
-        <v>-113325.97</v>
+        <v>-6848674.5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B205" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D205" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E205">
-        <v>17241.76</v>
+        <v>4.5</v>
       </c>
       <c r="G205">
-        <v>-130567.73</v>
+        <v>-6848679</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B206" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D206" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E206">
-        <v>10360.73</v>
+        <v>4590.5</v>
       </c>
       <c r="G206">
-        <v>-140928.46</v>
+        <v>-6853269.5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B207" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D207" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E207">
-        <v>37329.6</v>
+        <v>4.5</v>
       </c>
       <c r="G207">
-        <v>-178258.06</v>
+        <v>-6853274</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B208" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D208" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E208">
-        <v>21021.09</v>
+        <v>13049.2</v>
       </c>
       <c r="G208">
-        <v>-199279.15</v>
+        <v>-6866323.2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B209" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D209" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E209">
-        <v>3399.11</v>
+        <v>4.5</v>
       </c>
       <c r="G209">
-        <v>-202678.26</v>
+        <v>-6866327.7</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B210" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D210" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E210">
-        <v>7560.57</v>
+        <v>10967.54</v>
       </c>
       <c r="G210">
-        <v>-210238.83</v>
+        <v>-6877295.24</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B211" t="str">
-        <v>COMM ON SUNDRY DIRECT CREDIT</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D211" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E211">
-        <v>126</v>
+        <v>4.5</v>
       </c>
       <c r="G211">
-        <v>-210364.83</v>
+        <v>-6877299.74</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B212" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D212" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E212">
-        <v>5607.62</v>
+        <v>3854907.24</v>
       </c>
       <c r="G212">
-        <v>-215972.45</v>
+        <v>-10732206.98</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B213" t="str">
-        <v>CHEQUE WITHDRAWAL - LCY</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D213" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E213">
-        <v>104679.71</v>
+        <v>4.5</v>
       </c>
       <c r="G213">
-        <v>-320652.16</v>
+        <v>-10732211.48</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>22/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B214" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C214" t="str">
-        <v>/009SWI2191540006</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D214" t="str">
-        <v>22/09/2023</v>
-      </c>
-      <c r="F214">
-        <v>321137.16</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E214">
+        <v>44632.73</v>
       </c>
       <c r="G214">
-        <v>485</v>
+        <v>-10776844.21</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B215" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D215" t="str">
-        <v>25/09/2023</v>
-      </c>
-      <c r="F215">
-        <v>7606.2</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E215">
+        <v>4.5</v>
       </c>
       <c r="G215">
-        <v>-7121.2</v>
+        <v>-10776848.71</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B216" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D216" t="str">
-        <v>25/09/2023</v>
-      </c>
-      <c r="F216">
-        <v>38789.05</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E216">
+        <v>2413500.59</v>
       </c>
       <c r="G216">
-        <v>-45910.25</v>
+        <v>-13190349.3</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B217" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D217" t="str">
-        <v>25/09/2023</v>
-      </c>
-      <c r="F217">
-        <v>92770.64</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E217">
+        <v>4.5</v>
       </c>
       <c r="G217">
-        <v>-138680.89</v>
+        <v>-13190353.8</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B218" t="str">
-        <v>INWARD CLEARING : START PERFECT ENTERPRISE</v>
-      </c>
-      <c r="C218" t="str">
-        <v>/0096044232680001</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D218" t="str">
-        <v>25/09/2023</v>
-      </c>
-      <c r="F218">
-        <v>63529</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E218">
+        <v>2594.26</v>
       </c>
       <c r="G218">
-        <v>-202209.89</v>
+        <v>-13192948.06</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B219" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D219" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E219">
-        <v>35552.66</v>
+        <v>4.5</v>
       </c>
       <c r="G219">
-        <v>-237762.55</v>
+        <v>-13192952.56</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B220" t="str">
-        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D220" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E220">
-        <v>4310.82</v>
+        <v>2804.76</v>
       </c>
       <c r="G220">
-        <v>-242077.87</v>
+        <v>-13195757.32</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B221" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D221" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E221">
-        <v>2065.45</v>
+        <v>4.5</v>
       </c>
       <c r="G221">
-        <v>-244143.32</v>
+        <v>-13195761.82</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B222" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D222" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E222">
-        <v>569273.42</v>
+        <v>1339.42</v>
       </c>
       <c r="G222">
-        <v>-813421.24</v>
+        <v>-13197101.24</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B223" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D223" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E223">
-        <v>483808.64</v>
+        <v>4.5</v>
       </c>
       <c r="G223">
-        <v>-1297234.38</v>
+        <v>-13197105.74</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B224" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D224" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E224">
-        <v>126174.93</v>
+        <v>7756.05</v>
       </c>
       <c r="G224">
-        <v>-1423413.81</v>
+        <v>-13204861.79</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B225" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D225" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E225">
-        <v>6097.42</v>
+        <v>4.5</v>
       </c>
       <c r="G225">
-        <v>-1429515.73</v>
+        <v>-13204866.29</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B226" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D226" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E226">
-        <v>7951.85</v>
+        <v>6353.64</v>
       </c>
       <c r="G226">
-        <v>-1437472.08</v>
+        <v>-13211219.93</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B227" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D227" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E227">
-        <v>253500.23</v>
+        <v>4.5</v>
       </c>
       <c r="G227">
-        <v>-1690976.81</v>
+        <v>-13211224.43</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B228" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D228" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E228">
-        <v>102550.22</v>
+        <v>10013.5</v>
       </c>
       <c r="G228">
-        <v>-1793531.53</v>
+        <v>-13221237.93</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B229" t="str">
-        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D229" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E229">
-        <v>4463.24</v>
+        <v>4.5</v>
       </c>
       <c r="G229">
-        <v>-1797999.27</v>
+        <v>-13221242.43</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B230" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D230" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E230">
-        <v>583172.14</v>
+        <v>28880</v>
       </c>
       <c r="G230">
-        <v>-2381171.41</v>
+        <v>-13250122.43</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B231" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D231" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E231">
-        <v>769600.37</v>
+        <v>4.5</v>
       </c>
       <c r="G231">
-        <v>-3150776.28</v>
+        <v>-13250126.93</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B232" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C232" t="str">
-        <v>/009SWI2191540006</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D232" t="str">
-        <v>25/09/2023</v>
-      </c>
-      <c r="F232">
-        <v>3216125.11</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E232">
+        <v>35653</v>
       </c>
       <c r="G232">
-        <v>65344.33</v>
+        <v>-13285779.93</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B233" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D233" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E233">
-        <v>13241.33</v>
+        <v>4.5</v>
       </c>
       <c r="G233">
-        <v>52103</v>
+        <v>-13285784.43</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B234" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D234" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E234">
-        <v>100</v>
+        <v>4544.86</v>
       </c>
       <c r="G234">
-        <v>51998.5</v>
+        <v>-13290329.29</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B235" t="str">
-        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D235" t="str">
-        <v>25/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E235">
-        <v>51510</v>
+        <v>4.5</v>
       </c>
       <c r="G235">
-        <v>485</v>
+        <v>-13290333.79</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B236" t="str">
-        <v>INWARD CLEARING : ESM COMPANY LTD</v>
-      </c>
-      <c r="C236" t="str">
-        <v>/0096726232690003</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D236" t="str">
-        <v>26/09/2023</v>
-      </c>
-      <c r="F236">
-        <v>304213.12</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E236">
+        <v>48493.8</v>
       </c>
       <c r="G236">
-        <v>-303728.12</v>
+        <v>-13338827.59</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B237" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D237" t="str">
-        <v>26/09/2023</v>
-      </c>
-      <c r="F237">
-        <v>173933.38</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E237">
+        <v>4.5</v>
       </c>
       <c r="G237">
-        <v>-477661.5</v>
+        <v>-13338832.09</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B238" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D238" t="str">
-        <v>26/09/2023</v>
-      </c>
-      <c r="F238">
-        <v>175903.5</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E238">
+        <v>2421993.4</v>
       </c>
       <c r="G238">
-        <v>-653565</v>
+        <v>-15760825.49</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B239" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D239" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E239">
-        <v>4847.58</v>
+        <v>4.5</v>
       </c>
       <c r="G239">
-        <v>-658412.58</v>
+        <v>-15760829.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B240" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D240" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E240">
-        <v>12273.81</v>
+        <v>15142.85</v>
       </c>
       <c r="G240">
-        <v>-670686.39</v>
+        <v>-15775972.84</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B241" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D241" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E241">
-        <v>2941.62</v>
+        <v>4.5</v>
       </c>
       <c r="G241">
-        <v>-673628.01</v>
+        <v>-15775977.34</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B242" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D242" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E242">
-        <v>9362.7</v>
+        <v>4787.35</v>
       </c>
       <c r="G242">
-        <v>-682990.71</v>
+        <v>-15780764.69</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B243" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D243" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E243">
-        <v>5252</v>
+        <v>4.5</v>
       </c>
       <c r="G243">
-        <v>-688242.71</v>
+        <v>-15780769.19</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B244" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D244" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E244">
-        <v>45450</v>
+        <v>3474.47</v>
       </c>
       <c r="G244">
-        <v>-733692.71</v>
+        <v>-15784243.66</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B245" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D245" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E245">
-        <v>73307.94</v>
+        <v>4.5</v>
       </c>
       <c r="G245">
-        <v>-807000.65</v>
+        <v>-15784248.16</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B246" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D246" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E246">
-        <v>40448.4</v>
+        <v>25980.97</v>
       </c>
       <c r="G246">
-        <v>-847449.05</v>
+        <v>-15810229.13</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B247" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D247" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E247">
-        <v>100</v>
+        <v>4.5</v>
       </c>
       <c r="G247">
-        <v>-847549.05</v>
+        <v>-15810233.63</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B248" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D248" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E248">
-        <v>5257.55</v>
+        <v>8558.4</v>
       </c>
       <c r="G248">
-        <v>-852806.6</v>
+        <v>-15818792.03</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B249" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D249" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E249">
-        <v>3758.81</v>
+        <v>4.5</v>
       </c>
       <c r="G249">
-        <v>-856565.41</v>
+        <v>-15818796.53</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B250" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D250" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E250">
-        <v>11979.05</v>
+        <v>2687158.38</v>
       </c>
       <c r="G250">
-        <v>-868544.46</v>
+        <v>-18505954.91</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B251" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D251" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E251">
-        <v>291.94</v>
+        <v>4.5</v>
       </c>
       <c r="G251">
-        <v>-868836.4</v>
+        <v>-18505959.41</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B252" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D252" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E252">
-        <v>100</v>
+        <v>4041.14</v>
       </c>
       <c r="G252">
-        <v>-868936.4</v>
+        <v>-18510000.55</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B253" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D253" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E253">
-        <v>400</v>
+        <v>4.5</v>
       </c>
       <c r="G253">
-        <v>-869336.4</v>
+        <v>-18510005.05</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B254" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D254" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E254">
-        <v>2271291.88</v>
+        <v>8104.58</v>
       </c>
       <c r="G254">
-        <v>-3140628.28</v>
+        <v>-18518109.63</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B255" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D255" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E255">
-        <v>390659.34</v>
+        <v>4.5</v>
       </c>
       <c r="G255">
-        <v>-3531287.62</v>
+        <v>-18518114.13</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B256" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D256" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E256">
-        <v>208706.57</v>
+        <v>12328.5</v>
       </c>
       <c r="G256">
-        <v>-3739994.19</v>
+        <v>-18530442.63</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B257" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D257" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E257">
-        <v>12186166.95</v>
+        <v>4.5</v>
       </c>
       <c r="G257">
-        <v>-15926161.14</v>
+        <v>-18530447.13</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B258" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D258" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E258">
-        <v>87625.98</v>
+        <v>1796447.76</v>
       </c>
       <c r="G258">
-        <v>-16013787.12</v>
+        <v>-20326894.89</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B259" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D259" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E259">
-        <v>62690.83</v>
+        <v>4.5</v>
       </c>
       <c r="G259">
-        <v>-16076477.95</v>
+        <v>-20326899.39</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B260" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D260" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E260">
-        <v>79563.25</v>
+        <v>5605.5</v>
       </c>
       <c r="G260">
-        <v>-16156041.2</v>
+        <v>-20332504.89</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B261" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D261" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E261">
-        <v>100</v>
+        <v>4.5</v>
       </c>
       <c r="G261">
-        <v>-16156141.2</v>
+        <v>-20332509.39</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B262" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D262" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E262">
-        <v>3046065.44</v>
+        <v>4129.43</v>
       </c>
       <c r="G262">
-        <v>-19202206.64</v>
+        <v>-20336638.82</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B263" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D263" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E263">
-        <v>10932836.95</v>
+        <v>4.5</v>
       </c>
       <c r="G263">
-        <v>-30135043.59</v>
+        <v>-20336643.32</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B264" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D264" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E264">
-        <v>44796.52</v>
+        <v>9998.69</v>
       </c>
       <c r="G264">
-        <v>-30179840.11</v>
+        <v>-20346642.01</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B265" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D265" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E265">
-        <v>66678.26</v>
+        <v>4.5</v>
       </c>
       <c r="G265">
-        <v>-30246518.37</v>
+        <v>-20346646.51</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B266" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C266" t="str">
+        <v>/009SWI2191540006</v>
       </c>
       <c r="D266" t="str">
-        <v>26/09/2023</v>
-      </c>
-      <c r="E266">
-        <v>72088.75</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="F266">
+        <v>22480302.81</v>
       </c>
       <c r="G266">
-        <v>-30318607.12</v>
+        <v>2133656.3</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B267" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D267" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E267">
-        <v>77658.9</v>
+        <v>2776.14</v>
       </c>
       <c r="G267">
-        <v>-30396266.02</v>
+        <v>2130880.16</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B268" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D268" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E268">
-        <v>41321.74</v>
+        <v>4.5</v>
       </c>
       <c r="G268">
-        <v>-30437587.76</v>
+        <v>2130875.66</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B269" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D269" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E269">
-        <v>76138.46</v>
+        <v>3530.34</v>
       </c>
       <c r="G269">
-        <v>-30513726.22</v>
+        <v>2127345.32</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B270" t="str">
-        <v>DIRECT CREDIT OUTGOING</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D270" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E270">
-        <v>127215.75</v>
+        <v>4.5</v>
       </c>
       <c r="G270">
-        <v>-30640941.97</v>
+        <v>2127340.82</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>26/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B271" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C271" t="str">
-        <v>/009SWI2191540006</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D271" t="str">
-        <v>26/09/2023</v>
-      </c>
-      <c r="F271">
-        <v>30641426.97</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E271">
+        <v>2203.79</v>
       </c>
       <c r="G271">
-        <v>485</v>
+        <v>2125137.03</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>27/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B272" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D272" t="str">
-        <v>27/09/2023</v>
-      </c>
-      <c r="F272">
-        <v>4546.65</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E272">
+        <v>4.5</v>
       </c>
       <c r="G272">
-        <v>-4061.65</v>
+        <v>2125132.53</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>27/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B273" t="str">
-        <v>INWARD CLEARING : FEDEX IAS</v>
-      </c>
-      <c r="C273" t="str">
-        <v>/0096800232700001</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D273" t="str">
-        <v>27/09/2023</v>
-      </c>
-      <c r="F273">
-        <v>2413.16</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E273">
+        <v>76138.46</v>
       </c>
       <c r="G273">
-        <v>-6474.81</v>
+        <v>2048994.07</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>27/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B274" t="str">
-        <v>DIRECT CREDIT RETURN</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D274" t="str">
-        <v>27/09/2023</v>
-      </c>
-      <c r="F274">
-        <v>62690.83</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E274">
+        <v>4.5</v>
       </c>
       <c r="G274">
-        <v>56216.02</v>
+        <v>2048989.57</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>27/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B275" t="str">
-        <v>DIRECT CREDIT RETURN</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D275" t="str">
-        <v>27/09/2023</v>
-      </c>
-      <c r="F275">
-        <v>76138.46</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E275">
+        <v>3863.7</v>
       </c>
       <c r="G275">
-        <v>132354.48</v>
+        <v>2045125.87</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>27/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B276" t="str">
-        <v>INWARD CLEARING : KINGDOM EXIM GHANA</v>
-      </c>
-      <c r="C276" t="str">
-        <v>/0096797232700001</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D276" t="str">
-        <v>27/09/2023</v>
-      </c>
-      <c r="F276">
-        <v>1140745.85</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E276">
+        <v>4.5</v>
       </c>
       <c r="G276">
-        <v>-1008391.37</v>
+        <v>2045121.37</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>27/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B277" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C277" t="str">
-        <v>/009SWI2191540006</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D277" t="str">
-        <v>27/09/2023</v>
-      </c>
-      <c r="F277">
-        <v>1008876.37</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E277">
+        <v>1999804.36</v>
       </c>
       <c r="G277">
-        <v>485</v>
+        <v>45317.01</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B278" t="str">
-        <v>INWARD CLEARING EXPRESS</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D278" t="str">
-        <v>28/09/2023</v>
-      </c>
-      <c r="F278">
-        <v>119156.78</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E278">
+        <v>4.5</v>
       </c>
       <c r="G278">
-        <v>-118671.78</v>
+        <v>45312.51</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B279" t="str">
-        <v>INWARD CLEARING : M AND K GHANA LTD</v>
-      </c>
-      <c r="C279" t="str">
-        <v>/0096487232710001</v>
+        <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D279" t="str">
-        <v>28/09/2023</v>
-      </c>
-      <c r="F279">
-        <v>27757.13</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E279">
+        <v>5807.5</v>
       </c>
       <c r="G279">
-        <v>-146428.91</v>
+        <v>39505.01</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B280" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D280" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E280">
-        <v>328000.68</v>
+        <v>4.5</v>
       </c>
       <c r="G280">
-        <v>-474429.59</v>
+        <v>39500.51</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B281" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D281" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E281">
-        <v>156848.07</v>
+        <v>5568.31</v>
       </c>
       <c r="G281">
-        <v>-631282.16</v>
+        <v>33932.2</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B282" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D282" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E282">
-        <v>2196.2</v>
+        <v>4.5</v>
       </c>
       <c r="G282">
-        <v>-633482.86</v>
+        <v>33927.7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B283" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D283" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E283">
-        <v>47848.4</v>
+        <v>6424.15</v>
       </c>
       <c r="G283">
-        <v>-681335.76</v>
+        <v>27503.55</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B284" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D284" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E284">
-        <v>56724.84</v>
+        <v>4.5</v>
       </c>
       <c r="G284">
-        <v>-738065.1</v>
+        <v>27499.05</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B285" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D285" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E285">
-        <v>1340783.9</v>
+        <v>16453.35</v>
       </c>
       <c r="G285">
-        <v>-2078853.5</v>
+        <v>11045.7</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B286" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D286" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E286">
-        <v>172966.31</v>
+        <v>4.5</v>
       </c>
       <c r="G286">
-        <v>-2251824.31</v>
+        <v>11041.2</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B287" t="str">
         <v>ONLINE OUTGOING TRANSFER</v>
       </c>
       <c r="D287" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="E287">
-        <v>187678.64</v>
+        <v>10551.7</v>
       </c>
       <c r="G287">
-        <v>-2439507.45</v>
+        <v>489.5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>28/09/2023</v>
+        <v>20/09/2023</v>
       </c>
       <c r="B288" t="str">
-        <v>CALL TRANSACTIONS - CR</v>
-      </c>
-      <c r="C288" t="str">
-        <v>/009SWI2191540006</v>
+        <v>COMMISSION</v>
       </c>
       <c r="D288" t="str">
-        <v>28/09/2023</v>
-      </c>
-      <c r="F288">
-        <v>2801929.98</v>
+        <v>20/09/2023</v>
+      </c>
+      <c r="E288">
+        <v>4.5</v>
       </c>
       <c r="G288">
-        <v>362418.03</v>
+        <v>485</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>28/09/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="B289" t="str">
-        <v>ONLINE OUTGOING TRANSFER</v>
+        <v>DIRECT CREDIT OUTGOING</v>
       </c>
       <c r="D289" t="str">
-        <v>28/09/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="E289">
-        <v>361928.53</v>
+        <v>1717</v>
       </c>
       <c r="G289">
-        <v>489.5</v>
+        <v>-1232</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>28/09/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="B290" t="str">
-        <v>COMMISSION</v>
+        <v>DIRECT CREDIT OUTGOING</v>
       </c>
       <c r="D290" t="str">
-        <v>28/09/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="E290">
-        <v>4.5</v>
+        <v>2727</v>
       </c>
       <c r="G290">
-        <v>485</v>
+        <v>-3959</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>29/09/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="B291" t="str">
-        <v>INWARD CLEARING : ALHAJI SALIA ENTERPRISE LTD</v>
-      </c>
-      <c r="C291" t="str">
-        <v>/0096185232720001</v>
+        <v>DIRECT CREDIT OUTGOING</v>
       </c>
       <c r="D291" t="str">
-        <v>29/09/2023</v>
-      </c>
-      <c r="F291">
-        <v>869.78</v>
+        <v>22/09/2023</v>
+      </c>
+      <c r="E291">
+        <v>5959.01</v>
       </c>
       <c r="G291">
-        <v>-384.78</v>
+        <v>-9918.01</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>29/09/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="B292" t="str">
-        <v>SERVICE CHARGES 00001</v>
-      </c>
-      <c r="C292" t="str">
-        <v>/009COT4GHS</v>
+        <v>DIRECT CREDIT OUTGOING</v>
       </c>
       <c r="D292" t="str">
-        <v>01/10/2023</v>
+        <v>22/09/2023</v>
       </c>
       <c r="E292">
-        <v>750</v>
+        <v>4721.88</v>
       </c>
       <c r="G292">
-        <v>-1134.78</v>
+        <v>-14639.89</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B293" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D293" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E293">
+        <v>11647.82</v>
+      </c>
+      <c r="G293">
+        <v>-26287.71</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B294" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D294" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E294">
+        <v>8162.79</v>
+      </c>
+      <c r="G294">
+        <v>-34450.5</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B295" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D295" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E295">
+        <v>5731.08</v>
+      </c>
+      <c r="G295">
+        <v>-40181.58</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B296" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D296" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E296">
+        <v>3048.93</v>
+      </c>
+      <c r="G296">
+        <v>-43230.51</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B297" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D297" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E297">
+        <v>24835.34</v>
+      </c>
+      <c r="G297">
+        <v>-68065.85</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B298" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D298" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E298">
+        <v>43219.92</v>
+      </c>
+      <c r="G298">
+        <v>-111285.77</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B299" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D299" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E299">
+        <v>2040.2</v>
+      </c>
+      <c r="G299">
+        <v>-113325.97</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B300" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D300" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E300">
+        <v>17241.76</v>
+      </c>
+      <c r="G300">
+        <v>-130567.73</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B301" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D301" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E301">
+        <v>10360.73</v>
+      </c>
+      <c r="G301">
+        <v>-140928.46</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B302" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D302" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E302">
+        <v>37329.6</v>
+      </c>
+      <c r="G302">
+        <v>-178258.06</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B303" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D303" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E303">
+        <v>21021.09</v>
+      </c>
+      <c r="G303">
+        <v>-199279.15</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B304" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D304" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E304">
+        <v>3399.11</v>
+      </c>
+      <c r="G304">
+        <v>-202678.26</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B305" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D305" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E305">
+        <v>7560.57</v>
+      </c>
+      <c r="G305">
+        <v>-210238.83</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B306" t="str">
+        <v>COMM ON SUNDRY DIRECT CREDIT</v>
+      </c>
+      <c r="D306" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E306">
+        <v>126</v>
+      </c>
+      <c r="G306">
+        <v>-210364.83</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B307" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D307" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E307">
+        <v>5607.62</v>
+      </c>
+      <c r="G307">
+        <v>-215972.45</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B308" t="str">
+        <v>CHEQUE WITHDRAWAL - LCY</v>
+      </c>
+      <c r="D308" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="E308">
+        <v>104679.71</v>
+      </c>
+      <c r="G308">
+        <v>-320652.16</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="B309" t="str">
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C309" t="str">
+        <v>/009SWI2191540006</v>
+      </c>
+      <c r="D309" t="str">
+        <v>22/09/2023</v>
+      </c>
+      <c r="F309">
+        <v>321137.16</v>
+      </c>
+      <c r="G309">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B310" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D310" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="F310">
+        <v>7606.2</v>
+      </c>
+      <c r="G310">
+        <v>-7121.2</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B311" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D311" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="F311">
+        <v>38789.05</v>
+      </c>
+      <c r="G311">
+        <v>-45910.25</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B312" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D312" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="F312">
+        <v>92770.64</v>
+      </c>
+      <c r="G312">
+        <v>-138680.89</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B313" t="str">
+        <v>INWARD CLEARING : START PERFECT ENTERPRISE</v>
+      </c>
+      <c r="C313" t="str">
+        <v>/0096044232680001</v>
+      </c>
+      <c r="D313" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="F313">
+        <v>63529</v>
+      </c>
+      <c r="G313">
+        <v>-202209.89</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B314" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D314" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E314">
+        <v>35552.66</v>
+      </c>
+      <c r="G314">
+        <v>-237762.55</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B315" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D315" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E315">
+        <v>4.5</v>
+      </c>
+      <c r="G315">
+        <v>-237767.05</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B316" t="str">
+        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+      </c>
+      <c r="D316" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E316">
+        <v>4310.82</v>
+      </c>
+      <c r="G316">
+        <v>-242077.87</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B317" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D317" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E317">
+        <v>2065.45</v>
+      </c>
+      <c r="G317">
+        <v>-244143.32</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B318" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D318" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E318">
+        <v>4.5</v>
+      </c>
+      <c r="G318">
+        <v>-244147.82</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B319" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D319" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E319">
+        <v>569273.42</v>
+      </c>
+      <c r="G319">
+        <v>-813421.24</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B320" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D320" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E320">
+        <v>4.5</v>
+      </c>
+      <c r="G320">
+        <v>-813425.74</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B321" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D321" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E321">
+        <v>483808.64</v>
+      </c>
+      <c r="G321">
+        <v>-1297234.38</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B322" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D322" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E322">
+        <v>4.5</v>
+      </c>
+      <c r="G322">
+        <v>-1297238.88</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B323" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D323" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E323">
+        <v>126174.93</v>
+      </c>
+      <c r="G323">
+        <v>-1423413.81</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B324" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D324" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E324">
+        <v>4.5</v>
+      </c>
+      <c r="G324">
+        <v>-1423418.31</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B325" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D325" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E325">
+        <v>6097.42</v>
+      </c>
+      <c r="G325">
+        <v>-1429515.73</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B326" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D326" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E326">
+        <v>4.5</v>
+      </c>
+      <c r="G326">
+        <v>-1429520.23</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B327" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D327" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E327">
+        <v>7951.85</v>
+      </c>
+      <c r="G327">
+        <v>-1437472.08</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B328" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D328" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E328">
+        <v>4.5</v>
+      </c>
+      <c r="G328">
+        <v>-1437476.58</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D329" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E329">
+        <v>253500.23</v>
+      </c>
+      <c r="G329">
+        <v>-1690976.81</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B330" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D330" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E330">
+        <v>4.5</v>
+      </c>
+      <c r="G330">
+        <v>-1690981.31</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B331" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D331" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E331">
+        <v>102550.22</v>
+      </c>
+      <c r="G331">
+        <v>-1793531.53</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B332" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D332" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E332">
+        <v>4.5</v>
+      </c>
+      <c r="G332">
+        <v>-1793536.03</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B333" t="str">
+        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+      </c>
+      <c r="D333" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E333">
+        <v>4463.24</v>
+      </c>
+      <c r="G333">
+        <v>-1797999.27</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B334" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D334" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E334">
+        <v>583172.14</v>
+      </c>
+      <c r="G334">
+        <v>-2381171.41</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B335" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D335" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E335">
+        <v>4.5</v>
+      </c>
+      <c r="G335">
+        <v>-2381175.91</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B336" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D336" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E336">
+        <v>769600.37</v>
+      </c>
+      <c r="G336">
+        <v>-3150776.28</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B337" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D337" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E337">
+        <v>4.5</v>
+      </c>
+      <c r="G337">
+        <v>-3150780.78</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B338" t="str">
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C338" t="str">
+        <v>/009SWI2191540006</v>
+      </c>
+      <c r="D338" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="F338">
+        <v>3216125.11</v>
+      </c>
+      <c r="G338">
+        <v>65344.33</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B339" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D339" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E339">
+        <v>13241.33</v>
+      </c>
+      <c r="G339">
+        <v>52103</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B340" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D340" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E340">
+        <v>4.5</v>
+      </c>
+      <c r="G340">
+        <v>52098.5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B341" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D341" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E341">
+        <v>100</v>
+      </c>
+      <c r="G341">
+        <v>51998.5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B342" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D342" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E342">
+        <v>3.5</v>
+      </c>
+      <c r="G342">
+        <v>51995</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="B343" t="str">
+        <v>ACCOUNT TO ACCOUNT TRANSFER</v>
+      </c>
+      <c r="D343" t="str">
+        <v>25/09/2023</v>
+      </c>
+      <c r="E343">
+        <v>51510</v>
+      </c>
+      <c r="G343">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B344" t="str">
+        <v>INWARD CLEARING : ESM COMPANY LTD</v>
+      </c>
+      <c r="C344" t="str">
+        <v>/0096726232690003</v>
+      </c>
+      <c r="D344" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="F344">
+        <v>304213.12</v>
+      </c>
+      <c r="G344">
+        <v>-303728.12</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B345" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D345" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="F345">
+        <v>173933.38</v>
+      </c>
+      <c r="G345">
+        <v>-477661.5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B346" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D346" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="F346">
+        <v>175903.5</v>
+      </c>
+      <c r="G346">
+        <v>-653565</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B347" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D347" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E347">
+        <v>4847.58</v>
+      </c>
+      <c r="G347">
+        <v>-658412.58</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B348" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D348" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E348">
+        <v>12273.81</v>
+      </c>
+      <c r="G348">
+        <v>-670686.39</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B349" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D349" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E349">
+        <v>2941.62</v>
+      </c>
+      <c r="G349">
+        <v>-673628.01</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B350" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D350" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E350">
+        <v>9362.7</v>
+      </c>
+      <c r="G350">
+        <v>-682990.71</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B351" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D351" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E351">
+        <v>5252</v>
+      </c>
+      <c r="G351">
+        <v>-688242.71</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B352" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D352" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E352">
+        <v>45450</v>
+      </c>
+      <c r="G352">
+        <v>-733692.71</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B353" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D353" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E353">
+        <v>73307.94</v>
+      </c>
+      <c r="G353">
+        <v>-807000.65</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B354" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D354" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E354">
+        <v>40448.4</v>
+      </c>
+      <c r="G354">
+        <v>-847449.05</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B355" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D355" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E355">
+        <v>100</v>
+      </c>
+      <c r="G355">
+        <v>-847549.05</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B356" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D356" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E356">
+        <v>5257.55</v>
+      </c>
+      <c r="G356">
+        <v>-852806.6</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B357" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D357" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E357">
+        <v>3758.81</v>
+      </c>
+      <c r="G357">
+        <v>-856565.41</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B358" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D358" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E358">
+        <v>11979.05</v>
+      </c>
+      <c r="G358">
+        <v>-868544.46</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B359" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D359" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E359">
+        <v>291.94</v>
+      </c>
+      <c r="G359">
+        <v>-868836.4</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B360" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D360" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E360">
+        <v>100</v>
+      </c>
+      <c r="G360">
+        <v>-868936.4</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B361" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D361" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E361">
+        <v>400</v>
+      </c>
+      <c r="G361">
+        <v>-869336.4</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B362" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D362" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E362">
+        <v>2271291.88</v>
+      </c>
+      <c r="G362">
+        <v>-3140628.28</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B363" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D363" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E363">
+        <v>390659.34</v>
+      </c>
+      <c r="G363">
+        <v>-3531287.62</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B364" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D364" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E364">
+        <v>208706.57</v>
+      </c>
+      <c r="G364">
+        <v>-3739994.19</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B365" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D365" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E365">
+        <v>12186166.95</v>
+      </c>
+      <c r="G365">
+        <v>-15926161.14</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B366" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D366" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E366">
+        <v>87625.98</v>
+      </c>
+      <c r="G366">
+        <v>-16013787.12</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B367" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D367" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E367">
+        <v>62690.83</v>
+      </c>
+      <c r="G367">
+        <v>-16076477.95</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B368" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D368" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E368">
+        <v>79563.25</v>
+      </c>
+      <c r="G368">
+        <v>-16156041.2</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B369" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D369" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E369">
+        <v>100</v>
+      </c>
+      <c r="G369">
+        <v>-16156141.2</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B370" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D370" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E370">
+        <v>3046065.44</v>
+      </c>
+      <c r="G370">
+        <v>-19202206.64</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B371" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D371" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E371">
+        <v>10932836.95</v>
+      </c>
+      <c r="G371">
+        <v>-30135043.59</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B372" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D372" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E372">
+        <v>44796.52</v>
+      </c>
+      <c r="G372">
+        <v>-30179840.11</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B373" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D373" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E373">
+        <v>66678.26</v>
+      </c>
+      <c r="G373">
+        <v>-30246518.37</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B374" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D374" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E374">
+        <v>72088.75</v>
+      </c>
+      <c r="G374">
+        <v>-30318607.12</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B375" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D375" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E375">
+        <v>77658.9</v>
+      </c>
+      <c r="G375">
+        <v>-30396266.02</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B376" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D376" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E376">
+        <v>41321.74</v>
+      </c>
+      <c r="G376">
+        <v>-30437587.76</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B377" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D377" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E377">
+        <v>76138.46</v>
+      </c>
+      <c r="G377">
+        <v>-30513726.22</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B378" t="str">
+        <v>DIRECT CREDIT OUTGOING</v>
+      </c>
+      <c r="D378" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="E378">
+        <v>127215.75</v>
+      </c>
+      <c r="G378">
+        <v>-30640941.97</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="B379" t="str">
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C379" t="str">
+        <v>/009SWI2191540006</v>
+      </c>
+      <c r="D379" t="str">
+        <v>26/09/2023</v>
+      </c>
+      <c r="F379">
+        <v>30641426.97</v>
+      </c>
+      <c r="G379">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="B380" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D380" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="F380">
+        <v>4546.65</v>
+      </c>
+      <c r="G380">
+        <v>-4061.65</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="B381" t="str">
+        <v>INWARD CLEARING : FEDEX IAS</v>
+      </c>
+      <c r="C381" t="str">
+        <v>/0096800232700001</v>
+      </c>
+      <c r="D381" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="F381">
+        <v>2413.16</v>
+      </c>
+      <c r="G381">
+        <v>-6474.81</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="B382" t="str">
+        <v>DIRECT CREDIT RETURN</v>
+      </c>
+      <c r="D382" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="F382">
+        <v>62690.83</v>
+      </c>
+      <c r="G382">
+        <v>56216.02</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="B383" t="str">
+        <v>DIRECT CREDIT RETURN</v>
+      </c>
+      <c r="D383" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="F383">
+        <v>76138.46</v>
+      </c>
+      <c r="G383">
+        <v>132354.48</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="B384" t="str">
+        <v>INWARD CLEARING : KINGDOM EXIM GHANA</v>
+      </c>
+      <c r="C384" t="str">
+        <v>/0096797232700001</v>
+      </c>
+      <c r="D384" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="F384">
+        <v>1140745.85</v>
+      </c>
+      <c r="G384">
+        <v>-1008391.37</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="B385" t="str">
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C385" t="str">
+        <v>/009SWI2191540006</v>
+      </c>
+      <c r="D385" t="str">
+        <v>27/09/2023</v>
+      </c>
+      <c r="F385">
+        <v>1008876.37</v>
+      </c>
+      <c r="G385">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B386" t="str">
+        <v>INWARD CLEARING EXPRESS</v>
+      </c>
+      <c r="D386" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="F386">
+        <v>119156.78</v>
+      </c>
+      <c r="G386">
+        <v>-118671.78</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B387" t="str">
+        <v>INWARD CLEARING : M AND K GHANA LTD</v>
+      </c>
+      <c r="C387" t="str">
+        <v>/0096487232710001</v>
+      </c>
+      <c r="D387" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="F387">
+        <v>27757.13</v>
+      </c>
+      <c r="G387">
+        <v>-146428.91</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B388" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D388" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E388">
+        <v>328000.68</v>
+      </c>
+      <c r="G388">
+        <v>-474429.59</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B389" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D389" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E389">
+        <v>4.5</v>
+      </c>
+      <c r="G389">
+        <v>-474434.09</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B390" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D390" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E390">
+        <v>156848.07</v>
+      </c>
+      <c r="G390">
+        <v>-631282.16</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B391" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D391" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E391">
+        <v>4.5</v>
+      </c>
+      <c r="G391">
+        <v>-631286.66</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B392" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D392" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E392">
+        <v>2196.2</v>
+      </c>
+      <c r="G392">
+        <v>-633482.86</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B393" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D393" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E393">
+        <v>4.5</v>
+      </c>
+      <c r="G393">
+        <v>-633487.36</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B394" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D394" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E394">
+        <v>47848.4</v>
+      </c>
+      <c r="G394">
+        <v>-681335.76</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B395" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D395" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E395">
+        <v>4.5</v>
+      </c>
+      <c r="G395">
+        <v>-681340.26</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B396" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D396" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E396">
+        <v>56724.84</v>
+      </c>
+      <c r="G396">
+        <v>-738065.1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B397" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D397" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E397">
+        <v>4.5</v>
+      </c>
+      <c r="G397">
+        <v>-738069.6</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B398" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D398" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E398">
+        <v>1340783.9</v>
+      </c>
+      <c r="G398">
+        <v>-2078853.5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B399" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D399" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E399">
+        <v>4.5</v>
+      </c>
+      <c r="G399">
+        <v>-2078858</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B400" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D400" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E400">
+        <v>172966.31</v>
+      </c>
+      <c r="G400">
+        <v>-2251824.31</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B401" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D401" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E401">
+        <v>4.5</v>
+      </c>
+      <c r="G401">
+        <v>-2251828.81</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B402" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D402" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E402">
+        <v>187678.64</v>
+      </c>
+      <c r="G402">
+        <v>-2439507.45</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B403" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D403" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E403">
+        <v>4.5</v>
+      </c>
+      <c r="G403">
+        <v>-2439511.95</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B404" t="str">
+        <v>CALL TRANSACTIONS - CR</v>
+      </c>
+      <c r="C404" t="str">
+        <v>/009SWI2191540006</v>
+      </c>
+      <c r="D404" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="F404">
+        <v>2801929.98</v>
+      </c>
+      <c r="G404">
+        <v>362418.03</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B405" t="str">
+        <v>ONLINE OUTGOING TRANSFER</v>
+      </c>
+      <c r="D405" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E405">
+        <v>361928.53</v>
+      </c>
+      <c r="G405">
+        <v>489.5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="B406" t="str">
+        <v>COMMISSION</v>
+      </c>
+      <c r="D406" t="str">
+        <v>28/09/2023</v>
+      </c>
+      <c r="E406">
+        <v>4.5</v>
+      </c>
+      <c r="G406">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
         <v>29/09/2023</v>
       </c>
-      <c r="B293" t="str">
+      <c r="B407" t="str">
+        <v>INWARD CLEARING : ALHAJI SALIA ENTERPRISE LTD</v>
+      </c>
+      <c r="C407" t="str">
+        <v>/0096185232720001</v>
+      </c>
+      <c r="D407" t="str">
+        <v>29/09/2023</v>
+      </c>
+      <c r="F407">
+        <v>869.78</v>
+      </c>
+      <c r="G407">
+        <v>-384.78</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>29/09/2023</v>
+      </c>
+      <c r="B408" t="str">
+        <v>SERVICE CHARGES 00001</v>
+      </c>
+      <c r="C408" t="str">
+        <v>/009COT4GHS</v>
+      </c>
+      <c r="D408" t="str">
+        <v>01/10/2023</v>
+      </c>
+      <c r="E408">
+        <v>750</v>
+      </c>
+      <c r="G408">
+        <v>-1134.78</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>29/09/2023</v>
+      </c>
+      <c r="B409" t="str">
         <v>CALL TRANSACTIONS - CR</v>
       </c>
-      <c r="C293" t="str">
+      <c r="C409" t="str">
         <v>/009SWI2191540006</v>
       </c>
-      <c r="D293" t="str">
+      <c r="D409" t="str">
         <v>29/09/2023</v>
       </c>
-      <c r="F293">
+      <c r="F409">
         <v>869.78</v>
       </c>
-      <c r="G293">
+      <c r="G409">
         <v>-265</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G293"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G409"/>
   </ignoredErrors>
 </worksheet>
 </file>